--- a/data/vannmiljo_catch_metadata.xlsx
+++ b/data/vannmiljo_catch_metadata.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T13"/>
+  <dimension ref="A1:T74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -532,16 +532,16 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>28960</v>
+        <v>28251</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>002-28960</t>
+          <t>002-28251</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Rømua ved Lørenfallet - RØM1</t>
+          <t>Nitelva ved Åmot</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -586,12 +586,12 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>5110-07</t>
+          <t>5110-10</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Øyeren</t>
+          <t>Leira - Nitelva</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -606,36 +606,36 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>002-3659-R</t>
+          <t>002-3891-R</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>Rømua</t>
+          <t>Nedre Nitelva</t>
         </is>
       </c>
       <c r="R2" t="n">
-        <v>289429.5</v>
+        <v>280231.9011000004</v>
       </c>
       <c r="S2" t="n">
-        <v>6659838.300000001</v>
+        <v>6651352.624500001</v>
       </c>
       <c r="T2" t="n">
-        <v>201.6969865555108</v>
+        <v>483.6833356735306</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>29659</v>
+        <v>28253</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>002-29659</t>
+          <t>002-28253</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Leira ved Borgen bru</t>
+          <t>Nitelva ved Nitelva bru</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -700,36 +700,36 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>002-3384-R</t>
+          <t>002-3891-R</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>Leira nedstrøms Krokfoss</t>
+          <t>Nedre Nitelva</t>
         </is>
       </c>
       <c r="R3" t="n">
-        <v>282243.1870999997</v>
+        <v>278294.1993000004</v>
       </c>
       <c r="S3" t="n">
-        <v>6652300.5583</v>
+        <v>6653249.8379</v>
       </c>
       <c r="T3" t="n">
-        <v>664.551043758648</v>
+        <v>476.7564709074747</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>30578</v>
+        <v>28260</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>002-30578</t>
+          <t>002-28260</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Kjellerholen Nitelva</t>
+          <t>Leira ved Frogner</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -794,36 +794,36 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>002-1638-R</t>
+          <t>002-3384-R</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>Nitelva Slattum-Kjeller</t>
+          <t>Leira nedstrøms Krokfoss</t>
         </is>
       </c>
       <c r="R4" t="n">
-        <v>277314.1501000002</v>
+        <v>282600.0603</v>
       </c>
       <c r="S4" t="n">
-        <v>6655820.7501</v>
+        <v>6660596.602700001</v>
       </c>
       <c r="T4" t="n">
-        <v>348.6096295402878</v>
+        <v>616.441865685792</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>30584</v>
+        <v>28960</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>002-30584</t>
+          <t>002-28960</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Leira ved Leirsund</t>
+          <t>Rømua ved Lørenfallet - RØM1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -868,12 +868,12 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>5110-10</t>
+          <t>5110-07</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Leira - Nitelva</t>
+          <t>Øyeren</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -888,36 +888,36 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>002-3384-R</t>
+          <t>002-3659-R</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>Leira nedstrøms Krokfoss</t>
+          <t>Rømua</t>
         </is>
       </c>
       <c r="R5" t="n">
-        <v>281893.7116999999</v>
+        <v>289429.5</v>
       </c>
       <c r="S5" t="n">
-        <v>6657589.4682</v>
+        <v>6659838.300000001</v>
       </c>
       <c r="T5" t="n">
-        <v>620.6195600936246</v>
+        <v>201.6969865555108</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>30586</v>
+        <v>28964</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>002-30586</t>
+          <t>002-28964</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Rud Nitelva</t>
+          <t>Nitelva ved Åros bru</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -942,12 +942,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3224</t>
+          <t>3205</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Rælingen</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -982,36 +982,36 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>002-3891-R</t>
+          <t>002-1638-R</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>Nedre Nitelva</t>
+          <t>Nitelva Slattum-Kjeller</t>
         </is>
       </c>
       <c r="R6" t="n">
-        <v>279794.1101000002</v>
+        <v>275712.9351000004</v>
       </c>
       <c r="S6" t="n">
-        <v>6651907.0001</v>
+        <v>6656817.6031</v>
       </c>
       <c r="T6" t="n">
-        <v>480.5965336609618</v>
+        <v>320.7416416148291</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>30593</v>
+        <v>29657</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>002-30593</t>
+          <t>002-29657</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Jeksla ved Haugli, J14</t>
+          <t>Leira etter samløp med Tveia</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1036,12 +1036,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3205</t>
+          <t>3230</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Gjerdrum</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1076,36 +1076,36 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>002-599-R</t>
+          <t>002-3384-R</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Jeksla</t>
+          <t>Leira nedstrøms Krokfoss</t>
         </is>
       </c>
       <c r="R7" t="n">
-        <v>282918.8400999997</v>
+        <v>283828.6001000004</v>
       </c>
       <c r="S7" t="n">
-        <v>6658024.370100001</v>
+        <v>6670591.5601</v>
       </c>
       <c r="T7" t="n">
-        <v>15.22205296975372</v>
+        <v>476.454675701109</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>46599</v>
+        <v>29659</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>002-46599</t>
+          <t>002-29659</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sagelva ved Skjetten bro (F3)</t>
+          <t>Leira ved Borgen bru</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1170,36 +1170,36 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>002-3899-R</t>
+          <t>002-3384-R</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Fjellhamarelva - Sagelva</t>
+          <t>Leira nedstrøms Krokfoss</t>
         </is>
       </c>
       <c r="R8" t="n">
-        <v>277645.8565999996</v>
+        <v>282243.1870999997</v>
       </c>
       <c r="S8" t="n">
-        <v>6653484.1592</v>
+        <v>6652300.5583</v>
       </c>
       <c r="T8" t="n">
-        <v>108.8204832889213</v>
+        <v>664.551043758648</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>60929</v>
+        <v>30575</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>002-60929</t>
+          <t>002-30575</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Fossåa ved Sylta</t>
+          <t>Frogner Leira</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1244,12 +1244,12 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>5110-07</t>
+          <t>5110-10</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Øyeren</t>
+          <t>Leira - Nitelva</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1264,36 +1264,36 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>002-3685-R</t>
+          <t>002-3384-R</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Fossåa</t>
+          <t>Leira nedstrøms Krokfoss</t>
         </is>
       </c>
       <c r="R9" t="n">
-        <v>293655.0999999996</v>
+        <v>282586.7795000002</v>
       </c>
       <c r="S9" t="n">
-        <v>6656302.699999999</v>
+        <v>6660372.9059</v>
       </c>
       <c r="T9" t="n">
-        <v>128.6625675913123</v>
+        <v>616.8737133735269</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>60933</v>
+        <v>30578</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>002-60933</t>
+          <t>002-30578</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Gansåa nedstrøms Dalen RA</t>
+          <t>Kjellerholen Nitelva</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1338,12 +1338,12 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>5110-07</t>
+          <t>5110-10</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Øyeren</t>
+          <t>Leira - Nitelva</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1358,36 +1358,36 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>002-3655-R</t>
+          <t>002-1638-R</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Gansåa</t>
+          <t>Nitelva Slattum-Kjeller</t>
         </is>
       </c>
       <c r="R10" t="n">
-        <v>288509.2999999998</v>
+        <v>277314.1501000002</v>
       </c>
       <c r="S10" t="n">
-        <v>6642006.800000001</v>
+        <v>6655820.7501</v>
       </c>
       <c r="T10" t="n">
-        <v>25.3147533602231</v>
+        <v>348.6096295402878</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>60963</v>
+        <v>30584</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>002-60963</t>
+          <t>002-30584</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sloråa ved Bruvollen</t>
+          <t>Leira ved Leirsund</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>5110-07</t>
+          <t>5110-10</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Øyeren</t>
+          <t>Leira - Nitelva</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1452,36 +1452,36 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>002-3687-R</t>
+          <t>002-3384-R</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Sloråa</t>
+          <t>Leira nedstrøms Krokfoss</t>
         </is>
       </c>
       <c r="R11" t="n">
-        <v>296281.4000000004</v>
+        <v>281893.7116999999</v>
       </c>
       <c r="S11" t="n">
-        <v>6655378.5</v>
+        <v>6657589.4682</v>
       </c>
       <c r="T11" t="n">
-        <v>60.52279954386854</v>
+        <v>620.6195600936246</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>60964</v>
+        <v>30586</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>002-60964</t>
+          <t>002-30586</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Kauserudåa før samløp Sloråa</t>
+          <t>Rud Nitelva</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1506,12 +1506,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>3205</t>
+          <t>3224</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Rælingen</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1526,12 +1526,12 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>5110-07</t>
+          <t>5110-10</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Øyeren</t>
+          <t>Leira - Nitelva</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1546,116 +1546,5850 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>002-3692-R</t>
+          <t>002-3891-R</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Stensrudåa - Korsåa</t>
+          <t>Nedre Nitelva</t>
         </is>
       </c>
       <c r="R12" t="n">
-        <v>296282.7000000002</v>
+        <v>279794.1101000002</v>
       </c>
       <c r="S12" t="n">
-        <v>6655243.800000001</v>
+        <v>6651907.0001</v>
       </c>
       <c r="T12" t="n">
-        <v>56.7935599380449</v>
+        <v>480.5965336609618</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
+        <v>30590</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>002-30590</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Jeksla ved  Nygård</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>point</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Akershus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>3209</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Ullensaker</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Glommavassdraget/Hvaler og Singlefjorden</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>5110-10</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Leira - Nitelva</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>5110</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Glomma</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>002-599-R</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Jeksla</t>
+        </is>
+      </c>
+      <c r="R13" t="n">
+        <v>284340.0669</v>
+      </c>
+      <c r="S13" t="n">
+        <v>6663922.139699999</v>
+      </c>
+      <c r="T13" t="n">
+        <v>492.2859836379801</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>30593</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>002-30593</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Jeksla ved Haugli, J14</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>point</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Akershus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>3205</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Lillestrøm</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Glommavassdraget/Hvaler og Singlefjorden</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>5110-10</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Leira - Nitelva</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>5110</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Glomma</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>002-599-R</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Jeksla</t>
+        </is>
+      </c>
+      <c r="R14" t="n">
+        <v>282918.8400999997</v>
+      </c>
+      <c r="S14" t="n">
+        <v>6658024.370100001</v>
+      </c>
+      <c r="T14" t="n">
+        <v>15.22205296975372</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>38919</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>002-38919</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Helltjern nedre, utløp</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>point</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Akershus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>3205</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Lillestrøm</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Glommavassdraget/Hvaler og Singlefjorden</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>5110-07</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Øyeren</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>5110</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Glomma</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>002-3655-R</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Gansåa</t>
+        </is>
+      </c>
+      <c r="R15" t="n">
+        <v>292325.2825999996</v>
+      </c>
+      <c r="S15" t="n">
+        <v>6646838.877699999</v>
+      </c>
+      <c r="T15" t="n">
+        <v>10.21180230138583</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>38920</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>002-38920</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Helltjern øvre, utløp</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>point</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Akershus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>3205</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Lillestrøm</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Glommavassdraget/Hvaler og Singlefjorden</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>5110-07</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Øyeren</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>5110</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Glomma</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>002-3655-R</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>Gansåa</t>
+        </is>
+      </c>
+      <c r="R16" t="n">
+        <v>292930.1212999998</v>
+      </c>
+      <c r="S16" t="n">
+        <v>6647229.932700001</v>
+      </c>
+      <c r="T16" t="n">
+        <v>10.21180230138583</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>39357</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>002-39357</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Sloråa</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>point</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Akershus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>3228</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Nes</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Glommavassdraget/Hvaler og Singlefjorden</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>5110-07</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Øyeren</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>5110</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Glomma</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>002-3687-R</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>Sloråa</t>
+        </is>
+      </c>
+      <c r="R17" t="n">
+        <v>298657.6352000004</v>
+      </c>
+      <c r="S17" t="n">
+        <v>6658198.144300001</v>
+      </c>
+      <c r="T17" t="n">
+        <v>45.81850759887208</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>39541</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>002-39541</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Sloråa SLO 1</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>point</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Akershus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>3205</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Lillestrøm</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Glommavassdraget/Hvaler og Singlefjorden</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>5110-07</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Øyeren</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>5110</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Glomma</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>002-3687-R</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>Sloråa</t>
+        </is>
+      </c>
+      <c r="R18" t="n">
+        <v>296283.3773999996</v>
+      </c>
+      <c r="S18" t="n">
+        <v>6655367.7662</v>
+      </c>
+      <c r="T18" t="n">
+        <v>60.52279954386854</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>39543</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>002-39543</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Rømua ved Kauserud mølle</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>point</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Akershus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>3209</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Ullensaker</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Glommavassdraget/Hvaler og Singlefjorden</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>5110-07</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Øyeren</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>5110</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Glomma</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>002-3659-R</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>Rømua</t>
+        </is>
+      </c>
+      <c r="R19" t="n">
+        <v>292445.5999999996</v>
+      </c>
+      <c r="S19" t="n">
+        <v>6666787.5</v>
+      </c>
+      <c r="T19" t="n">
+        <v>91.46633927201819</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>39545</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>002-39545</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Bekk til Øyern Gansdalen GAN 1</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>point</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Akershus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>3205</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Lillestrøm</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Glommavassdraget/Hvaler og Singlefjorden</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>5110-07</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Øyeren</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>5110</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Glomma</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>002-3655-R</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>Gansåa</t>
+        </is>
+      </c>
+      <c r="R20" t="n">
+        <v>288657.3805</v>
+      </c>
+      <c r="S20" t="n">
+        <v>6642454.7557</v>
+      </c>
+      <c r="T20" t="n">
+        <v>21.46306963423563</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>39546</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>002-39546</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Bekk til Øyern Gansdalen DAL 1</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>point</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Akershus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>3205</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Lillestrøm</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Glommavassdraget/Hvaler og Singlefjorden</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>5110-07</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Øyeren</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>5110</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Glomma</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>002-3655-R</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>Gansåa</t>
+        </is>
+      </c>
+      <c r="R21" t="n">
+        <v>288680.9283999996</v>
+      </c>
+      <c r="S21" t="n">
+        <v>6642099.419600001</v>
+      </c>
+      <c r="T21" t="n">
+        <v>21.45667153143251</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>46599</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>002-46599</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Sagelva ved Skjetten bro (F3)</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>point</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Akershus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>3205</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Lillestrøm</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Glommavassdraget/Hvaler og Singlefjorden</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>5110-10</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Leira - Nitelva</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>5110</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Glomma</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>002-3899-R</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>Fjellhamarelva - Sagelva</t>
+        </is>
+      </c>
+      <c r="R22" t="n">
+        <v>277645.8565999996</v>
+      </c>
+      <c r="S22" t="n">
+        <v>6653484.1592</v>
+      </c>
+      <c r="T22" t="n">
+        <v>108.8204832889213</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>60835</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>002-60835</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Rømua ved Onsrud - RØM2</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>point</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Akershus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>3209</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Ullensaker</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Glommavassdraget/Hvaler og Singlefjorden</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>5110-07</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Øyeren</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>5110</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Glomma</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>002-3659-R</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>Rømua</t>
+        </is>
+      </c>
+      <c r="R23" t="n">
+        <v>293540.9000000004</v>
+      </c>
+      <c r="S23" t="n">
+        <v>6671605.5</v>
+      </c>
+      <c r="T23" t="n">
+        <v>45.33754587764441</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>60929</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>002-60929</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Fossåa ved Sylta</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>point</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Akershus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>3205</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Lillestrøm</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Glommavassdraget/Hvaler og Singlefjorden</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>5110-07</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Øyeren</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>5110</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Glomma</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>002-3685-R</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>Fossåa</t>
+        </is>
+      </c>
+      <c r="R24" t="n">
+        <v>293655.0999999996</v>
+      </c>
+      <c r="S24" t="n">
+        <v>6656302.699999999</v>
+      </c>
+      <c r="T24" t="n">
+        <v>128.6625675913123</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>60930</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>002-60930</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Storåa - ÅA3</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>point</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Akershus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>3205</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Lillestrøm</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Glommavassdraget/Hvaler og Singlefjorden</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>5110-07</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Øyeren</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>5110</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Glomma</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>002-3685-R</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>Fossåa</t>
+        </is>
+      </c>
+      <c r="R25" t="n">
+        <v>296238.7000000002</v>
+      </c>
+      <c r="S25" t="n">
+        <v>6655318.800000001</v>
+      </c>
+      <c r="T25" t="n">
+        <v>57.07989965721545</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>60932</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>002-60932</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Slora ved Kurland (Åa5)</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>point</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Akershus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>3205</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Lillestrøm</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Glommavassdraget/Hvaler og Singlefjorden</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>5110-07</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Øyeren</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>5110</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Glomma</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>002-3687-R</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>Sloråa</t>
+        </is>
+      </c>
+      <c r="R26" t="n">
+        <v>298098.2435999997</v>
+      </c>
+      <c r="S26" t="n">
+        <v>6657607.630100001</v>
+      </c>
+      <c r="T26" t="n">
+        <v>56.22930230272725</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>60933</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>002-60933</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Gansåa nedstrøms Dalen RA</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>point</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Akershus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>3205</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Lillestrøm</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Glommavassdraget/Hvaler og Singlefjorden</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>5110-07</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Øyeren</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>5110</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Glomma</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>002-3655-R</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>Gansåa</t>
+        </is>
+      </c>
+      <c r="R27" t="n">
+        <v>288509.2999999998</v>
+      </c>
+      <c r="S27" t="n">
+        <v>6642006.800000001</v>
+      </c>
+      <c r="T27" t="n">
+        <v>25.3147533602231</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>60963</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>002-60963</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Sloråa ved Bruvollen</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>point</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Akershus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>3205</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Lillestrøm</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Glommavassdraget/Hvaler og Singlefjorden</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>5110-07</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Øyeren</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>5110</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Glomma</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>002-3687-R</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>Sloråa</t>
+        </is>
+      </c>
+      <c r="R28" t="n">
+        <v>296281.4000000004</v>
+      </c>
+      <c r="S28" t="n">
+        <v>6655378.5</v>
+      </c>
+      <c r="T28" t="n">
+        <v>60.52279954386854</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>60964</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>002-60964</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Kauserudåa før samløp Sloråa</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>point</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Akershus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>3205</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Lillestrøm</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Glommavassdraget/Hvaler og Singlefjorden</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>5110-07</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Øyeren</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>5110</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Glomma</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>002-3692-R</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>Stensrudåa - Korsåa</t>
+        </is>
+      </c>
+      <c r="R29" t="n">
+        <v>296282.7000000002</v>
+      </c>
+      <c r="S29" t="n">
+        <v>6655243.800000001</v>
+      </c>
+      <c r="T29" t="n">
+        <v>56.7935599380449</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>62190</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>002-62190</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Nitelva</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>point</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Akershus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>3205</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Lillestrøm</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Glommavassdraget/Hvaler og Singlefjorden</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>5110-10</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Leira - Nitelva</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>5110</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Glomma</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>002-3891-R</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>Nedre Nitelva</t>
+        </is>
+      </c>
+      <c r="R30" t="n">
+        <v>280401.9968999997</v>
+      </c>
+      <c r="S30" t="n">
+        <v>6651558.4825</v>
+      </c>
+      <c r="T30" t="n">
+        <v>483.6833356735306</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>62191</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>002-62191</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Nitelva</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>point</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Akershus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>3205</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Lillestrøm</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Glommavassdraget/Hvaler og Singlefjorden</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>5110-10</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Leira - Nitelva</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>5110</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Glomma</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>002-3891-R</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>Nedre Nitelva</t>
+        </is>
+      </c>
+      <c r="R31" t="n">
+        <v>280363.9254999999</v>
+      </c>
+      <c r="S31" t="n">
+        <v>6651511.6304</v>
+      </c>
+      <c r="T31" t="n">
+        <v>483.6833356735306</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>62192</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>002-62192</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Nitelva</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>point</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Akershus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>3205</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Lillestrøm</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Glommavassdraget/Hvaler og Singlefjorden</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>5110-10</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Leira - Nitelva</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>5110</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Glomma</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>002-3891-R</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>Nedre Nitelva</t>
+        </is>
+      </c>
+      <c r="R32" t="n">
+        <v>280334.7829</v>
+      </c>
+      <c r="S32" t="n">
+        <v>6651464.247300001</v>
+      </c>
+      <c r="T32" t="n">
+        <v>483.6833356735306</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>62193</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>002-62193</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Nitelva</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>point</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Akershus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>3205</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Lillestrøm</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Glommavassdraget/Hvaler og Singlefjorden</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>5110-10</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Leira - Nitelva</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>5110</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Glomma</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>002-3891-R</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>Nedre Nitelva</t>
+        </is>
+      </c>
+      <c r="R33" t="n">
+        <v>280277.6018000003</v>
+      </c>
+      <c r="S33" t="n">
+        <v>6651416.3005</v>
+      </c>
+      <c r="T33" t="n">
+        <v>483.6833356735306</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>62194</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>002-62194</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Nitelva</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>point</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Akershus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>3205</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Lillestrøm</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Glommavassdraget/Hvaler og Singlefjorden</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>5110-10</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Leira - Nitelva</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>5110</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Glomma</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>002-3891-R</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>Nedre Nitelva</t>
+        </is>
+      </c>
+      <c r="R34" t="n">
+        <v>280186.4134</v>
+      </c>
+      <c r="S34" t="n">
+        <v>6651446.287699999</v>
+      </c>
+      <c r="T34" t="n">
+        <v>483.5361920257999</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
         <v>63540</v>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>002-63540</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>Fjellhammarelva (F10)</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>point</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>Akershus</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>3205</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>Lillestrøm</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t>002</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t>Glommavassdraget/Hvaler og Singlefjorden</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="L35" t="inlineStr">
         <is>
           <t>5110-10</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t>Leira - Nitelva</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="N35" t="inlineStr">
         <is>
           <t>5110</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="O35" t="inlineStr">
         <is>
           <t>Glomma</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="P35" t="inlineStr">
         <is>
           <t>002-3899-R</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="Q35" t="inlineStr">
         <is>
           <t>Fjellhamarelva - Sagelva</t>
         </is>
       </c>
-      <c r="R13" t="n">
+      <c r="R35" t="n">
         <v>276390.4391999999</v>
       </c>
-      <c r="S13" t="n">
+      <c r="S35" t="n">
         <v>6651962.844799999</v>
       </c>
-      <c r="T13" t="n">
+      <c r="T35" t="n">
         <v>104.836566299955</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>79086</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>002-79086</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Leira, Kråkfoss</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>point</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Akershus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>3209</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Ullensaker</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Glommavassdraget/Hvaler og Singlefjorden</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>5110-10</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Leira - Nitelva</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>5110</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Glomma</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>002-3384-R</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>Leira nedstrøms Krokfoss</t>
+        </is>
+      </c>
+      <c r="R36" t="n">
+        <v>282325.2884999998</v>
+      </c>
+      <c r="S36" t="n">
+        <v>6672584.819</v>
+      </c>
+      <c r="T36" t="n">
+        <v>431.0473562425867</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>79089</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>002-79089</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Leira (Eidsvoll)</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>point</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Akershus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>3205</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Lillestrøm</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Glommavassdraget/Hvaler og Singlefjorden</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>5110-10</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Leira - Nitelva</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>5110</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Glomma</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>002-3384-R</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>Leira nedstrøms Krokfoss</t>
+        </is>
+      </c>
+      <c r="R37" t="n">
+        <v>282597.9703000002</v>
+      </c>
+      <c r="S37" t="n">
+        <v>6661229.2478</v>
+      </c>
+      <c r="T37" t="n">
+        <v>614.260263820485</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>79092</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>002-79092</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Nitelva, Rud</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>point</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Akershus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>3224</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Rælingen</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Glommavassdraget/Hvaler og Singlefjorden</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>5110-10</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Leira - Nitelva</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>5110</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Glomma</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>002-3891-R</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>Nedre Nitelva</t>
+        </is>
+      </c>
+      <c r="R38" t="n">
+        <v>279601.3443999998</v>
+      </c>
+      <c r="S38" t="n">
+        <v>6652108.3654</v>
+      </c>
+      <c r="T38" t="n">
+        <v>479.9695813145062</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>79097</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>002-79097</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Fjellhammarelva, Sagdalen</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>point</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Akershus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>3205</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Lillestrøm</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Glommavassdraget/Hvaler og Singlefjorden</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>5110-10</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Leira - Nitelva</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>5110</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Glomma</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>002-3899-R</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>Fjellhamarelva - Sagelva</t>
+        </is>
+      </c>
+      <c r="R39" t="n">
+        <v>277527.8452000003</v>
+      </c>
+      <c r="S39" t="n">
+        <v>6653329.321599999</v>
+      </c>
+      <c r="T39" t="n">
+        <v>107.1603902733104</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>79557</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>002-79557</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Leira, Tveia</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>point</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Akershus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>3209</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Ullensaker</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Glommavassdraget/Hvaler og Singlefjorden</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>5110-10</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>Leira - Nitelva</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>5110</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>Glomma</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>002-3384-R</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>Leira nedstrøms Krokfoss</t>
+        </is>
+      </c>
+      <c r="R40" t="n">
+        <v>284066.9409999996</v>
+      </c>
+      <c r="S40" t="n">
+        <v>6670487.7926</v>
+      </c>
+      <c r="T40" t="n">
+        <v>476.7201848256024</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>80573</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>002-80573</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Nitelva</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>point</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Akershus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>3224</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Rælingen</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Glommavassdraget/Hvaler og Singlefjorden</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>5110-10</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>Leira - Nitelva</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>5110</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Glomma</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>002-3891-R</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>Nedre Nitelva</t>
+        </is>
+      </c>
+      <c r="R41" t="n">
+        <v>280382.1688000001</v>
+      </c>
+      <c r="S41" t="n">
+        <v>6651131.0045</v>
+      </c>
+      <c r="T41" t="n">
+        <v>483.8160849656666</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>81594</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>002-81594</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Nitelva</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>point</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Akershus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>3205</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Lillestrøm</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Glommavassdraget/Hvaler og Singlefjorden</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>5110-10</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>Leira - Nitelva</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>5110</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>Glomma</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>002-3891-R</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>Nedre Nitelva</t>
+        </is>
+      </c>
+      <c r="R42" t="n">
+        <v>280074.0999999996</v>
+      </c>
+      <c r="S42" t="n">
+        <v>6651633.300000001</v>
+      </c>
+      <c r="T42" t="n">
+        <v>482.7269057366076</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>81595</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>002-81595</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Nitelva</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>point</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Akershus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>3224</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Rælingen</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Glommavassdraget/Hvaler og Singlefjorden</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>5110-10</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>Leira - Nitelva</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>5110</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>Glomma</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>002-3891-R</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>Nedre Nitelva</t>
+        </is>
+      </c>
+      <c r="R43" t="n">
+        <v>280550.9903999995</v>
+      </c>
+      <c r="S43" t="n">
+        <v>6650921.41</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1152.013782477569</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>91322</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>002-91322</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>MJØ1</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>point</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Akershus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>3205</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Lillestrøm</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Glommavassdraget/Hvaler og Singlefjorden</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>5110-07</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>Øyeren</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>5110</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>Glomma</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>002-3655-R</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>Gansåa</t>
+        </is>
+      </c>
+      <c r="R44" t="n">
+        <v>291950</v>
+      </c>
+      <c r="S44" t="n">
+        <v>6645223</v>
+      </c>
+      <c r="T44" t="n">
+        <v>12.45915984287273</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>94483</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>002-94483</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Jekslabekken</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>point</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Akershus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>3205</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Lillestrøm</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Glommavassdraget/Hvaler og Singlefjorden</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>5110-10</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>Leira - Nitelva</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>5110</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>Glomma</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>002-599-R</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>Jeksla</t>
+        </is>
+      </c>
+      <c r="R45" t="n">
+        <v>282474.4000000004</v>
+      </c>
+      <c r="S45" t="n">
+        <v>6657544.4</v>
+      </c>
+      <c r="T45" t="n">
+        <v>16.95584348734277</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>98385</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>002-98385</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO1, Brånåsdalen avfallsdeponi, resipient overvåkning </t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>point</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Akershus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>3205</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Lillestrøm</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Glommavassdraget/Hvaler og Singlefjorden</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>5110-10</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>Leira - Nitelva</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>5110</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>Glomma</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>002-1638-R</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>Nitelva Slattum-Kjeller</t>
+        </is>
+      </c>
+      <c r="R46" t="n">
+        <v>277467.1261</v>
+      </c>
+      <c r="S46" t="n">
+        <v>6655804.919</v>
+      </c>
+      <c r="T46" t="n">
+        <v>348.6480139272359</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>98386</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>002-98386</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NN1, Brånåsdalen avfallsdeponi, resipient overvåkning </t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>point</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Akershus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>3205</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Lillestrøm</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Glommavassdraget/Hvaler og Singlefjorden</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>5110-10</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>Leira - Nitelva</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>5110</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>Glomma</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>002-3891-R</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>Nedre Nitelva</t>
+        </is>
+      </c>
+      <c r="R47" t="n">
+        <v>277556.7061000001</v>
+      </c>
+      <c r="S47" t="n">
+        <v>6655795.767200001</v>
+      </c>
+      <c r="T47" t="n">
+        <v>351.9906607814055</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>101949</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>002-101949</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Fjellhamarelva oppstr. Vittenbergbekken</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>point</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Akershus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>3222</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Lørenskog</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Glommavassdraget/Hvaler og Singlefjorden</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>5110-10</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>Leira - Nitelva</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>5110</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>Glomma</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>002-3899-R</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>Fjellhamarelva - Sagelva</t>
+        </is>
+      </c>
+      <c r="R48" t="n">
+        <v>276267.7389000002</v>
+      </c>
+      <c r="S48" t="n">
+        <v>6651912.9143</v>
+      </c>
+      <c r="T48" t="n">
+        <v>96.74708161883802</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>106796</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>002-106796</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gansbekken </t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>point</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Akershus</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>3205</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Lillestrøm</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Glommavassdraget/Hvaler og Singlefjorden</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>5110-07</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>Øyeren</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>5110</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>Glomma</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>002-3655-R</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>Gansåa</t>
+        </is>
+      </c>
+      <c r="R49" t="n">
+        <v>288571</v>
+      </c>
+      <c r="S49" t="n">
+        <v>6642086.9</v>
+      </c>
+      <c r="T49" t="n">
+        <v>25.27476522733575</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>106815</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>002-106815</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Sloråa - SLO</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>point</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Akershus</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>3205</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Lillestrøm</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Glommavassdraget/Hvaler og Singlefjorden</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>5110-07</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>Øyeren</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>5110</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>Glomma</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>002-3687-R</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>Sloråa</t>
+        </is>
+      </c>
+      <c r="R50" t="n">
+        <v>296276.8857000005</v>
+      </c>
+      <c r="S50" t="n">
+        <v>6655354.779100001</v>
+      </c>
+      <c r="T50" t="n">
+        <v>57.07989965721545</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>106818</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>002-106818</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Kauserudåa - KAU</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>point</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Akershus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>3205</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Lillestrøm</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Glommavassdraget/Hvaler og Singlefjorden</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>5110-07</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>Øyeren</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>5110</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>Glomma</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>002-3692-R</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>Stensrudåa - Korsåa</t>
+        </is>
+      </c>
+      <c r="R51" t="n">
+        <v>296279.6772999996</v>
+      </c>
+      <c r="S51" t="n">
+        <v>6655265.265900001</v>
+      </c>
+      <c r="T51" t="n">
+        <v>56.7935599380449</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>109603</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>002-109603</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Fossåa ved utløp Glomma/Fossdammen</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>point</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Akershus</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>3205</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Lillestrøm</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Glommavassdraget/Hvaler og Singlefjorden</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>5110-07</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>Øyeren</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>5110</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>Glomma</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>002-3685-R</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>Fossåa</t>
+        </is>
+      </c>
+      <c r="R52" t="n">
+        <v>293127.5703999996</v>
+      </c>
+      <c r="S52" t="n">
+        <v>6656661.7137</v>
+      </c>
+      <c r="T52" t="n">
+        <v>130.4589290145577</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>109604</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>002-109604</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Fossåa - strykparti ved Mo</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>point</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Akershus</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>3205</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Lillestrøm</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Glommavassdraget/Hvaler og Singlefjorden</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>5110-07</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>Øyeren</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>5110</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>Glomma</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>002-3685-R</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>Fossåa</t>
+        </is>
+      </c>
+      <c r="R53" t="n">
+        <v>295340.7781999996</v>
+      </c>
+      <c r="S53" t="n">
+        <v>6655159.9037</v>
+      </c>
+      <c r="T53" t="n">
+        <v>118.4025207172987</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>109608</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>002-109608</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Rømua oppstrøms Slemdalsfossen</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>point</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Akershus</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>3205</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Lillestrøm</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Glommavassdraget/Hvaler og Singlefjorden</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>5110-07</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>Øyeren</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>5110</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>Glomma</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>002-3659-R</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>Rømua</t>
+        </is>
+      </c>
+      <c r="R54" t="n">
+        <v>291432.9356000004</v>
+      </c>
+      <c r="S54" t="n">
+        <v>6665847.4581</v>
+      </c>
+      <c r="T54" t="n">
+        <v>93.92490028792476</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>111393</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>002-111393</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Nedstrøms Leira</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>point</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Akershus</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>3205</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Lillestrøm</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Glommavassdraget/Hvaler og Singlefjorden</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>5110-10</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>Leira - Nitelva</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>5110</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>Glomma</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>002-3384-R</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>Leira nedstrøms Kråkfoss</t>
+        </is>
+      </c>
+      <c r="R55" t="n">
+        <v>282548.4099000003</v>
+      </c>
+      <c r="S55" t="n">
+        <v>6661315.6504</v>
+      </c>
+      <c r="T55" t="n">
+        <v>614.2170793560676</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>112453</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>002-112453</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Fossåa - FOS</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>point</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Akershus</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>3205</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Lillestrøm</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Glommavassdraget/Hvaler og Singlefjorden</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>5110-07</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>Øyeren</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>5110</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>Glomma</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>002-3685-R</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>Fossåa</t>
+        </is>
+      </c>
+      <c r="R56" t="n">
+        <v>293645.5</v>
+      </c>
+      <c r="S56" t="n">
+        <v>6656315.6</v>
+      </c>
+      <c r="T56" t="n">
+        <v>128.6625675913123</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>112458</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>002-112458</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Jekslabekken</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>point</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Akershus</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>3205</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Lillestrøm</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Glommavassdraget/Hvaler og Singlefjorden</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>5110-10</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>Leira - Nitelva</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>5110</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>Glomma</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>002-599-R</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>Jeksla</t>
+        </is>
+      </c>
+      <c r="R57" t="n">
+        <v>283954.2542000003</v>
+      </c>
+      <c r="S57" t="n">
+        <v>6660089.3028</v>
+      </c>
+      <c r="T57" t="n">
+        <v>10.07820844918792</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>112459</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>002-112459</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Gislebekken</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>point</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Akershus</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>3205</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Lillestrøm</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Glommavassdraget/Hvaler og Singlefjorden</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>5110-10</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>Leira - Nitelva</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>5110</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>Glomma</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>002-599-R</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>Jeksla</t>
+        </is>
+      </c>
+      <c r="R58" t="n">
+        <v>284038.6870999997</v>
+      </c>
+      <c r="S58" t="n">
+        <v>6663365.059</v>
+      </c>
+      <c r="T58" t="n">
+        <v>493.109690507017</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>112480</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>002-112480</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Sagelva 3</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>point</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Akershus</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>3222</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Lørenskog</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Glommavassdraget/Hvaler og Singlefjorden</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>5110-10</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>Leira - Nitelva</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>5110</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>Glomma</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>002-3899-R</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>Fjellhamarelva - Sagelva</t>
+        </is>
+      </c>
+      <c r="R59" t="n">
+        <v>276291.2999999998</v>
+      </c>
+      <c r="S59" t="n">
+        <v>6651918.4</v>
+      </c>
+      <c r="T59" t="n">
+        <v>96.74708161883802</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>112482</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>002-112482</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Sagelva 1</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>point</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Akershus</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>3205</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Lillestrøm</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Glommavassdraget/Hvaler og Singlefjorden</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>5110-10</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>Leira - Nitelva</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>5110</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>Glomma</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>002-3899-R</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>Fjellhamarelva - Sagelva</t>
+        </is>
+      </c>
+      <c r="R60" t="n">
+        <v>277611.9397999998</v>
+      </c>
+      <c r="S60" t="n">
+        <v>6653463.604699999</v>
+      </c>
+      <c r="T60" t="n">
+        <v>108.8028905586008</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>116279</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>002-116279</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Rømua v. Nedre Lund</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>point</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Akershus</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>3209</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Ullensaker</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Glommavassdraget/Hvaler og Singlefjorden</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>5110-07</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>Øyeren</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>5110</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>Glomma</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>002-3659-R</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>Rømua</t>
+        </is>
+      </c>
+      <c r="R61" t="n">
+        <v>292903.0669</v>
+      </c>
+      <c r="S61" t="n">
+        <v>6669122.148</v>
+      </c>
+      <c r="T61" t="n">
+        <v>51.08014384705691</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>116769</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>002-116769</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Sagelva Gisledalen</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>point</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Akershus</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>3205</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Lillestrøm</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Glommavassdraget/Hvaler og Singlefjorden</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>5110-10</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>Leira - Nitelva</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>5110</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>Glomma</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>002-3899-R</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>Fjellhamarelva - Sagelva</t>
+        </is>
+      </c>
+      <c r="R62" t="n">
+        <v>277576.5146000003</v>
+      </c>
+      <c r="S62" t="n">
+        <v>6653446.939099999</v>
+      </c>
+      <c r="T62" t="n">
+        <v>108.8028905586008</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>116770</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>002-116770</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Sagelva Flåen bru</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>point</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Akershus</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>3205</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Lillestrøm</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Glommavassdraget/Hvaler og Singlefjorden</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>5110-10</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>Leira - Nitelva</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>5110</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>Glomma</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>002-3899-R</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>Fjellhamarelva - Sagelva</t>
+        </is>
+      </c>
+      <c r="R63" t="n">
+        <v>277327.5011</v>
+      </c>
+      <c r="S63" t="n">
+        <v>6652977.7541</v>
+      </c>
+      <c r="T63" t="n">
+        <v>106.8549184682515</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>116773</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>002-116773</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Sagelva nedstrøms Slora</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>point</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Akershus</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>3205</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Lillestrøm</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Glommavassdraget/Hvaler og Singlefjorden</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>5110-10</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>Leira - Nitelva</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>5110</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>Glomma</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>002-3899-R</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>Fjellhamarelva - Sagelva</t>
+        </is>
+      </c>
+      <c r="R64" t="n">
+        <v>276674.2180000003</v>
+      </c>
+      <c r="S64" t="n">
+        <v>6652212.823799999</v>
+      </c>
+      <c r="T64" t="n">
+        <v>105.3995265382286</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>116775</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>002-116775</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Sagelva Slora</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>point</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Akershus</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>3205</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Lillestrøm</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Glommavassdraget/Hvaler og Singlefjorden</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>5110-10</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>Leira - Nitelva</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>5110</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>Glomma</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>002-3899-R</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>Fjellhamarelva - Sagelva</t>
+        </is>
+      </c>
+      <c r="R65" t="n">
+        <v>276463.7422000002</v>
+      </c>
+      <c r="S65" t="n">
+        <v>6652076.819499999</v>
+      </c>
+      <c r="T65" t="n">
+        <v>105.2188029829524</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>116831</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>002-116831</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Fjellhamarelva før samløp Losbyelva</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>point</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Akershus</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>3222</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Lørenskog</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Glommavassdraget/Hvaler og Singlefjorden</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>5110-10</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>Leira - Nitelva</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>5110</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>Glomma</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>002-3899-R</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>Fjellhamarelva - Sagelva</t>
+        </is>
+      </c>
+      <c r="R66" t="n">
+        <v>274856.3766000001</v>
+      </c>
+      <c r="S66" t="n">
+        <v>6650717.587400001</v>
+      </c>
+      <c r="T66" t="n">
+        <v>38.4042855769802</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>117737</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>002-117737</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Fjellhammarelva før dam</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>point</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Akershus</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>3222</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Lørenskog</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Glommavassdraget/Hvaler og Singlefjorden</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>5110-10</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>Leira - Nitelva</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>5110</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>Glomma</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>002-3899-R</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>Fjellhamarelva - Sagelva</t>
+        </is>
+      </c>
+      <c r="R67" t="n">
+        <v>275752.0665999996</v>
+      </c>
+      <c r="S67" t="n">
+        <v>6651036.271199999</v>
+      </c>
+      <c r="T67" t="n">
+        <v>95.053416651216</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>122192</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>002-122192</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Oppstrøms Leira</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>point</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Akershus</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>3205</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Lillestrøm</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Glommavassdraget/Hvaler og Singlefjorden</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>5110-10</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>Leira - Nitelva</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>5110</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>Glomma</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>002-3384-R</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>Leira nedstrøms Kråkfoss</t>
+        </is>
+      </c>
+      <c r="R68" t="n">
+        <v>282541.8326000003</v>
+      </c>
+      <c r="S68" t="n">
+        <v>6661337.8519</v>
+      </c>
+      <c r="T68" t="n">
+        <v>614.2170793560676</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>125315</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>002-125315</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>6 Bekk fra Asakenga</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>point</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Akershus</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>3205</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Lillestrøm</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Glommavassdraget/Hvaler og Singlefjorden</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>5110-07</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>Øyeren</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>5110</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>Glomma</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>002-3659-R</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>Rømua</t>
+        </is>
+      </c>
+      <c r="R69" t="n">
+        <v>289436</v>
+      </c>
+      <c r="S69" t="n">
+        <v>6661338</v>
+      </c>
+      <c r="T69" t="n">
+        <v>169.1705364062334</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>125320</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>002-125320</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>A4-22 Overvannsrør ved RØM1</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>point</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Akershus</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>3205</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Lillestrøm</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Glommavassdraget/Hvaler og Singlefjorden</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>5110-07</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>Øyeren</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>5110</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>Glomma</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>002-3659-R</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>Rømua</t>
+        </is>
+      </c>
+      <c r="R70" t="n">
+        <v>289447</v>
+      </c>
+      <c r="S70" t="n">
+        <v>6659799</v>
+      </c>
+      <c r="T70" t="n">
+        <v>201.7081832984445</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>125322</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>002-125322</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>8 Rømua oppstrøms Asakbekken ved Asakenga/hestesenter</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>point</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Akershus</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>3205</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Lillestrøm</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Glommavassdraget/Hvaler og Singlefjorden</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>5110-07</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>Øyeren</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>5110</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>Glomma</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>002-3659-R</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>Rømua</t>
+        </is>
+      </c>
+      <c r="R71" t="n">
+        <v>289592</v>
+      </c>
+      <c r="S71" t="n">
+        <v>6661539</v>
+      </c>
+      <c r="T71" t="n">
+        <v>168.8266341571218</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>125505</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>002-125505</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>KAU</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>point</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Akershus</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>3205</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Lillestrøm</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Glommavassdraget/Hvaler og Singlefjorden</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>5110-07</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>Øyeren</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>5110</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>Glomma</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>002-3692-R</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>Stensrudåa - Korsåa</t>
+        </is>
+      </c>
+      <c r="R72" t="n">
+        <v>296284</v>
+      </c>
+      <c r="S72" t="n">
+        <v>6655258</v>
+      </c>
+      <c r="T72" t="n">
+        <v>56.7935599380449</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>126657</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>002-126657</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Nitelva oppstrøms Ringnes</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>point</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Akershus</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>3232</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Nittedal</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Glommavassdraget/Hvaler og Singlefjorden</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>5110-10</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>Leira - Nitelva</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>5110</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>Glomma</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>002-1638-R</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>Nitelva Slattum-Kjeller</t>
+        </is>
+      </c>
+      <c r="R73" t="n">
+        <v>273611.3154999996</v>
+      </c>
+      <c r="S73" t="n">
+        <v>6658038.509400001</v>
+      </c>
+      <c r="T73" t="n">
+        <v>315.6719144351956</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>126658</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>002-126658</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Nitelva nedstrøms Ringnes</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>point</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Akershus</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>3232</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Nittedal</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Glommavassdraget/Hvaler og Singlefjorden</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>5110-10</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>Leira - Nitelva</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>5110</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>Glomma</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>002-1638-R</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>Nitelva Slattum-Kjeller</t>
+        </is>
+      </c>
+      <c r="R74" t="n">
+        <v>273755.4035</v>
+      </c>
+      <c r="S74" t="n">
+        <v>6657807.770199999</v>
+      </c>
+      <c r="T74" t="n">
+        <v>316.2700390134703</v>
       </c>
     </row>
   </sheetData>
